--- a/APIs.xlsx
+++ b/APIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kayto\Desktop\IT\Projects\Stage\Stage PFE\Visit_Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73F9A6DA-0B92-4784-A3C8-07F71A55969D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56622867-C07B-46E9-B907-B8303CAD7CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{DF0767DB-063E-4B1E-8577-6D93F461A514}"/>
+    <workbookView xWindow="-16320" yWindow="-1335" windowWidth="16440" windowHeight="28320" xr2:uid="{DF0767DB-063E-4B1E-8577-6D93F461A514}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="80">
   <si>
     <t>Endpoint</t>
   </si>
@@ -116,18 +116,9 @@
     <t>Create timesheet with visits</t>
   </si>
   <si>
-    <t>{ weekNumber: 9, year: 2025, supervisorID: "user_001", visits: [...] }</t>
-  </si>
-  <si>
-    <t>Created timesheet</t>
-  </si>
-  <si>
     <t>List all timesheets</t>
   </si>
   <si>
-    <t>[Timesheet objects]</t>
-  </si>
-  <si>
     <t>/api/timesheets/:id</t>
   </si>
   <si>
@@ -137,9 +128,6 @@
     <t>:id = ts_001</t>
   </si>
   <si>
-    <t>Timesheet with visits</t>
-  </si>
-  <si>
     <t>/api/timesheets/:id/validate</t>
   </si>
   <si>
@@ -152,9 +140,6 @@
     <t>{ visitIDs: ["vis_001"], status: "validated" }</t>
   </si>
   <si>
-    <t>Updated timesheet</t>
-  </si>
-  <si>
     <t>/api/timesheets/supervisor/:supervisorID</t>
   </si>
   <si>
@@ -173,9 +158,6 @@
     <t>Create a new visit</t>
   </si>
   <si>
-    <t>{ date: "2025-03-06", time: "09:00", agentID: "agent_001", ... }</t>
-  </si>
-  <si>
     <t>Created visit</t>
   </si>
   <si>
@@ -197,9 +179,6 @@
     <t>Log visit details</t>
   </si>
   <si>
-    <t>{ duration: 45, checklistUpdates: { "chk_001": true } }</t>
-  </si>
-  <si>
     <t>Updated visit</t>
   </si>
   <si>
@@ -212,9 +191,6 @@
     <t>:id = vis_001</t>
   </si>
   <si>
-    <t>Visit with checklist/reasons</t>
-  </si>
-  <si>
     <t>Checklist Endpoints</t>
   </si>
   <si>
@@ -236,9 +212,6 @@
     <t>Get checklists by visit ID</t>
   </si>
   <si>
-    <t>[Checklist items]</t>
-  </si>
-  <si>
     <t>Reason Endpoints</t>
   </si>
   <si>
@@ -260,14 +233,610 @@
     <t>Get reasons by visit ID</t>
   </si>
   <si>
-    <t>[Reason items]</t>
+    <t>{
+  "weekNumber": 9,
+  "year": 2025,
+  "supervisorID": "user_001",
+  "visits": [
+    {
+      "date": "2025-03-08",
+      "time": "09:00:00",
+      "agentID": "agent_001",
+      "reasons": [
+        { "text": "item test" },
+        { "id": "rea_001" }
+      ],
+      "checklists": [
+        { "id": "chk_001" },
+        { "text": "item text" }
+      ]
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{  "duration": 45,  "checklistUpdates": [    { "checklistID": "chk_003", "checked": true }  ]}</t>
+  </si>
+  <si>
+    <t>List All Checklists</t>
+  </si>
+  <si>
+    <t>List All Reasons</t>
+  </si>
+  <si>
+    <t>[
+    {
+        "reasonID": "rea_001",
+        "item": "Routine inspection",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z"
+    },
+    {
+        "reasonID": "rea_002",
+        "item": "Complaint investigation",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z"
+    },
+    {
+        "reasonID": "rea_003",
+        "item": "Training session",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z"
+    }
+]</t>
+  </si>
+  <si>
+    <t>[
+    {
+        "checklistID": "chk_001",
+        "item": "Verify store inventory",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z"
+    },
+    {
+        "checklistID": "chk_002",
+        "item": "Check security cameras",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z"
+    },
+    {
+        "checklistID": "chk_003",
+        "item": "Confirm staff presence",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z"
+    }
+]</t>
+  </si>
+  <si>
+    <t>[
+    {
+        "checklistID": "chk_001",
+        "item": "Verify store inventory",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z",
+        "VisitChecklist": {
+            "checked": false,
+            "createdAt": "2025-03-08T10:41:10.178Z",
+            "updatedAt": "2025-03-08T10:41:10.178Z",
+            "visitID": "vis_001",
+            "checklistID": "chk_001"
+        }
+    },
+    {
+        "checklistID": "chk_002",
+        "item": "Check security cameras",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z",
+        "VisitChecklist": {
+            "checked": false,
+            "createdAt": "2025-03-08T10:41:10.178Z",
+            "updatedAt": "2025-03-08T10:41:10.178Z",
+            "visitID": "vis_001",
+            "checklistID": "chk_002"
+        }
+    }
+]</t>
+  </si>
+  <si>
+    <t>[
+    {
+        "reasonID": "rea_003",
+        "item": "Training session",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z",
+        "VisitReasons": {
+            "createdAt": "2025-03-08T10:41:10.178Z",
+            "updatedAt": "2025-03-08T10:41:10.178Z",
+            "visitID": "vis_003",
+            "reasonID": "rea_003"
+        }
+    }
+]</t>
+  </si>
+  <si>
+    <t>{
+    "visitID": "vis_001",
+    "date": "2025-03-06",
+    "time": "09:00:00",
+    "duration": 45,
+    "location": "Casablanca",
+    "status": "visited",
+    "photos": [
+        "photo1.jpg",
+        "photo2.jpg"
+    ],
+    "comment": "Routine check completed",
+    "agentID": "agent_001",
+    "timesheetID": "ts_001",
+    "createdAt": "2025-03-08T10:41:10.178Z",
+    "updatedAt": "2025-03-08T12:16:42.605Z",
+    "Checklists": [
+        {
+            "checklistID": "chk_001",
+            "item": "Verify store inventory",
+            "createdAt": "2025-03-08T10:41:10.178Z",
+            "updatedAt": "2025-03-08T10:41:10.178Z",
+            "VisitChecklist": {
+                "checked": false,
+                "createdAt": "2025-03-08T10:41:10.178Z",
+                "updatedAt": "2025-03-08T10:41:10.178Z",
+                "visitID": "vis_001",
+                "checklistID": "chk_001"
+            }
+        },
+        {
+            "checklistID": "chk_002",
+            "item": "Check security cameras",
+            "createdAt": "2025-03-08T10:41:10.178Z",
+            "updatedAt": "2025-03-08T10:41:10.178Z",
+            "VisitChecklist": {
+                "checked": false,
+                "createdAt": "2025-03-08T10:41:10.178Z",
+                "updatedAt": "2025-03-08T10:41:10.178Z",
+                "visitID": "vis_001",
+                "checklistID": "chk_002"
+            }
+        }
+    ],
+    "Reasons": [
+        {
+            "reasonID": "rea_001",
+            "item": "Routine inspection",
+            "createdAt": "2025-03-08T10:41:10.178Z",
+            "updatedAt": "2025-03-08T10:41:10.178Z",
+            "VisitReasons": {
+                "createdAt": "2025-03-08T10:41:10.178Z",
+                "updatedAt": "2025-03-08T10:41:10.178Z",
+                "visitID": "vis_001",
+                "reasonID": "rea_001"
+            }
+        }
+    ]
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {
+        "timesheetID" : "ts_001",
+        "supervisorID" : "user_001",
+      "date": "2025-03-08",
+      "time": "09:00:00",
+      "agentID": "agent_001",
+      "reasons": [
+        { "text": "item test" },
+        { "id": "rea_001" }
+      ],
+      "checklists": [
+        { "id": "chk_001" },
+        { "text": "item text" }
+      ]
+    }</t>
+  </si>
+  <si>
+    <t>[
+    {
+        "timesheetID": "ts_003",
+        "weekNumber": 9,
+        "year": 2025,
+        "status": "pending",
+        "supervisorID": "user_001",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z",
+        "Visits": [
+            {
+                "visitID": "vis_003",
+                "date": "2025-03-06",
+                "time": "14:00:00",
+                "duration": 60,
+                "location": "Marrakech",
+                "status": "pending",
+                "photos": [],
+                "comment": "Training session scheduled",
+                "agentID": "agent_003",
+                "timesheetID": "ts_003",
+                "createdAt": "2025-03-08T10:41:10.178Z",
+                "updatedAt": "2025-03-08T10:41:10.178Z",
+                "Checklists": [
+                    {
+                        "item": "Verify store inventory",
+                        "VisitChecklist": {
+                            "checked": false
+                        }
+                    }
+                ],
+                "Reasons": [
+                    {
+                        "item": "Training session"
+                    }
+                ]
+            }
+        ]
+    },
+    {
+        "timesheetID": "ts_001",
+        "weekNumber": 9,
+        "year": 2025,
+        "status": "validated",
+        "supervisorID": "user_001",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T12:16:42.620Z",
+        "Visits": [
+            {
+                "visitID": "vis_001",
+                "date": "2025-03-06",
+                "time": "09:00:00",
+                "duration": 45,
+                "location": "Casablanca",
+                "status": "visited",
+                "photos": [
+                    "photo1.jpg",
+                    "photo2.jpg"
+                ],
+                "comment": "Routine check completed",
+                "agentID": "agent_001",
+                "timesheetID": "ts_001",
+                "createdAt": "2025-03-08T10:41:10.178Z",
+                "updatedAt": "2025-03-08T13:42:22.320Z",
+                "Checklists": [
+                    {
+                        "item": "Verify store inventory",
+                        "VisitChecklist": {
+                            "checked": true
+                        }
+                    },
+                    {
+                        "item": "Check security cameras",
+                        "VisitChecklist": {
+                            "checked": false
+                        }
+                    }
+                ],
+                "Reasons": [
+                    {
+                        "item": "Routine inspection"
+                    }
+                ]
+            },
+            {
+                "visitID": "vis_oSjFe9A2zFGXkn9kDVh9G",
+                "date": "2025-03-08",
+                "time": "09:00:00",
+                "duration": null,
+                "location": "Casablanca",
+                "status": "pending",
+                "photos": [],
+                "comment": null,
+                "agentID": "agent_001",
+                "timesheetID": "ts_001",
+                "createdAt": "2025-03-08T13:45:38.782Z",
+                "updatedAt": "2025-03-08T13:45:38.782Z",
+                "Checklists": [
+                    {
+                        "item": "Verify store inventory",
+                        "VisitChecklist": {
+                            "checked": false
+                        }
+                    },
+                    {
+                        "item": "item text",
+                        "VisitChecklist": {
+                            "checked": false
+                        }
+                    }
+                ],
+                "Reasons": [
+                    {
+                        "item": "Routine inspection"
+                    },
+                    {
+                        "item": "item test"
+                    }
+                ]
+            }
+        ]
+    }
+]</t>
+  </si>
+  <si>
+    <t>{
+    "timesheetID": "ts_001",
+    "weekNumber": 9,
+    "year": 2025,
+    "status": "validated",
+    "supervisorID": "user_001",
+    "createdAt": "2025-03-08T10:41:10.178Z",
+    "updatedAt": "2025-03-08T12:16:42.620Z"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "timesheetID": "ts_001",
+    "weekNumber": 9,
+    "year": 2025,
+    "status": "validated",
+    "supervisorID": "user_001",
+    "createdAt": "2025-03-08T10:41:10.178Z",
+    "updatedAt": "2025-03-08T12:16:42.620Z",
+    "Visits": [
+        {
+            "visitID": "vis_001",
+            "date": "2025-03-06",
+            "time": "09:00:00",
+            "duration": 45,
+            "location": "Casablanca",
+            "status": "validated",
+            "photos": [
+                "photo1.jpg",
+                "photo2.jpg"
+            ],
+            "comment": "Routine check completed",
+            "agentID": "agent_001",
+            "timesheetID": "ts_001",
+            "createdAt": "2025-03-08T10:41:10.178Z",
+            "updatedAt": "2025-03-08T13:47:29.861Z",
+            "Checklists": [
+                {
+                    "item": "Verify store inventory",
+                    "VisitChecklist": {
+                        "checked": true
+                    }
+                },
+                {
+                    "item": "Check security cameras",
+                    "VisitChecklist": {
+                        "checked": false
+                    }
+                }
+            ],
+            "Reasons": [
+                {
+                    "item": "Routine inspection"
+                }
+            ]
+        },
+        {
+            "visitID": "vis_oSjFe9A2zFGXkn9kDVh9G",
+            "date": "2025-03-08",
+            "time": "09:00:00",
+            "duration": null,
+            "location": "Casablanca",
+            "status": "pending",
+            "photos": [],
+            "comment": null,
+            "agentID": "agent_001",
+            "timesheetID": "ts_001",
+            "createdAt": "2025-03-08T13:45:38.782Z",
+            "updatedAt": "2025-03-08T13:45:38.782Z",
+            "Checklists": [
+                {
+                    "item": "Verify store inventory",
+                    "VisitChecklist": {
+                        "checked": false
+                    }
+                },
+                {
+                    "item": "item text",
+                    "VisitChecklist": {
+                        "checked": false
+                    }
+                }
+            ],
+            "Reasons": [
+                {
+                    "item": "Routine inspection"
+                },
+                {
+                    "item": "item test"
+                }
+            ]
+        }
+    ]
+}</t>
+  </si>
+  <si>
+    <t>[
+    {
+        "timesheetID": "ts_001",
+        "weekNumber": 9,
+        "year": 2025,
+        "status": "validated",
+        "supervisorID": "user_001",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T12:16:42.620Z",
+        "Visits": [
+            {
+                "visitID": "vis_001",
+                "date": "2025-03-06",
+                "time": "09:00:00",
+                "duration": 45,
+                "location": "Casablanca",
+                "status": "validated",
+                "photos": [
+                    "photo1.jpg",
+                    "photo2.jpg"
+                ],
+                "comment": "Routine check completed",
+                "agentID": "agent_001",
+                "timesheetID": "ts_001",
+                "createdAt": "2025-03-08T10:41:10.178Z",
+                "updatedAt": "2025-03-08T13:47:29.861Z",
+                "Checklists": [
+                    {
+                        "item": "Verify store inventory",
+                        "VisitChecklist": {
+                            "checked": true
+                        }
+                    },
+                    {
+                        "item": "Check security cameras",
+                        "VisitChecklist": {
+                            "checked": false
+                        }
+                    }
+                ],
+                "Reasons": [
+                    {
+                        "item": "Routine inspection"
+                    }
+                ]
+            },
+            {
+                "visitID": "vis_oSjFe9A2zFGXkn9kDVh9G",
+                "date": "2025-03-08",
+                "time": "09:00:00",
+                "duration": null,
+                "location": "Casablanca",
+                "status": "pending",
+                "photos": [],
+                "comment": null,
+                "agentID": "agent_001",
+                "timesheetID": "ts_001",
+                "createdAt": "2025-03-08T13:45:38.782Z",
+                "updatedAt": "2025-03-08T13:45:38.782Z",
+                "Checklists": [
+                    {
+                        "item": "Verify store inventory",
+                        "VisitChecklist": {
+                            "checked": false
+                        }
+                    },
+                    {
+                        "item": "item text",
+                        "VisitChecklist": {
+                            "checked": false
+                        }
+                    }
+                ],
+                "Reasons": [
+                    {
+                        "item": "Routine inspection"
+                    },
+                    {
+                        "item": "item test"
+                    }
+                ]
+            }
+        ]
+    },
+    {
+        "timesheetID": "ts_002",
+        "weekNumber": 9,
+        "year": 2025,
+        "status": "validated",
+        "supervisorID": "user_002",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z",
+        "Visits": [
+            {
+                "visitID": "vis_002",
+                "date": "2025-03-06",
+                "time": "10:30:00",
+                "duration": 45,
+                "location": "Rabat",
+                "status": "visited",
+                "photos": [
+                    "photo3.jpg"
+                ],
+                "comment": "Security check passed",
+                "agentID": "agent_002",
+                "timesheetID": "ts_002",
+                "createdAt": "2025-03-08T10:41:10.178Z",
+                "updatedAt": "2025-03-08T13:10:21.745Z",
+                "Checklists": [
+                    {
+                        "item": "Confirm staff presence",
+                        "VisitChecklist": {
+                            "checked": true
+                        }
+                    }
+                ],
+                "Reasons": [
+                    {
+                        "item": "Complaint investigation"
+                    }
+                ]
+            }
+        ]
+    },
+    {
+        "timesheetID": "ts_003",
+        "weekNumber": 9,
+        "year": 2025,
+        "status": "pending",
+        "supervisorID": "user_001",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z",
+        "Visits": [
+            {
+                "visitID": "vis_003",
+                "date": "2025-03-06",
+                "time": "14:00:00",
+                "duration": 60,
+                "location": "Marrakech",
+                "status": "pending",
+                "photos": [],
+                "comment": "Training session scheduled",
+                "agentID": "agent_003",
+                "timesheetID": "ts_003",
+                "createdAt": "2025-03-08T10:41:10.178Z",
+                "updatedAt": "2025-03-08T10:41:10.178Z",
+                "Checklists": [
+                    {
+                        "item": "Verify store inventory",
+                        "VisitChecklist": {
+                            "checked": false
+                        }
+                    }
+                ],
+                "Reasons": [
+                    {
+                        "item": "Training session"
+                    }
+                ]
+            }
+        ]
+    }
+]</t>
+  </si>
+  <si>
+    <t>{
+    "message": "Timesheet created successfully",
+    "timesheet": {
+        "timesheetID": "ts_003",
+        "weekNumber": 9,
+        "year": 2025,
+        "status": "pending",
+        "supervisorID": "user_001",
+        "createdAt": "2025-03-08T10:41:10.178Z",
+        "updatedAt": "2025-03-08T10:41:10.178Z"
+    }
+}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,6 +891,11 @@
       <color rgb="FF133819"/>
       <name val="Ui-sans-serif"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Ui-monospace"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -349,7 +923,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -597,11 +1171,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF742932"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF742932"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF742932"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -718,6 +1340,36 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1054,17 +1706,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77AFA0F-72FB-4DB8-A725-CC0BF3CB3F86}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.42578125" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="58.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1">
+    <row r="1" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1185,10 +1837,10 @@
         <v>25</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" thickBot="1">
@@ -1199,69 +1851,69 @@
         <v>7</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A11" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A13" s="12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A14" s="22" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
@@ -1270,75 +1922,75 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A16" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A17" s="12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A19" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1347,82 +1999,117 @@
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A20" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" thickBot="1">
+      <c r="A21" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1" thickBot="1">
+      <c r="A22" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1" thickBot="1">
+      <c r="A23" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1" thickBot="1">
+      <c r="A24" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="E24" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="17" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1" thickBot="1">
+      <c r="A25" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" customHeight="1" thickBot="1">
+      <c r="A26" s="35" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A21" s="12" t="s">
+      <c r="B26" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" thickBot="1">
-      <c r="A24" s="35" t="s">
+      <c r="D26" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="39" t="s">
         <v>72</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>